--- a/analiz_rabochee_mesto_sentyabr_2026.xlsx
+++ b/analiz_rabochee_mesto_sentyabr_2026.xlsx
@@ -1943,15 +1943,15 @@
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="6" t="n"/>
     </row>
-    <row r="51" ht="48" customHeight="1">
+    <row r="51" ht="56" customHeight="1">
       <c r="B51" s="43" t="inlineStr">
         <is>
-          <t>Ночь 31.08–01.09</t>
+          <t>31.08–01.09 ночная (пн–вт)</t>
         </is>
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>Журнал начинается уже с выхода из чистой зоны в 05:09:25. Сколько сотрудник провёл на рабочем месте до этого момента, неизвестно. После возвращения в 05:44:19 он был в чистой зоне ещё 3 ч 15 мин 20 сек и вышел в 08:59:39 — на 21 сек раньше 09:00. Этот фрагмент не входит в общий итог времени.</t>
+          <t>В журнале только окончание ночной смены: нет входа через турникет и неизвестно, когда сотрудник впервые зашёл в чистую зону. Время на рабочем месте до выхода в 05:09:25 не посчитано. Выход из чистой зоны в 08:59:39 — на 21 сек раньше 09:00. Это меньше одной минуты и как нарушение не выделено.</t>
         </is>
       </c>
       <c r="D51" s="45" t="n"/>
@@ -1959,15 +1959,15 @@
       <c r="F51" s="45" t="n"/>
       <c r="G51" s="45" t="n"/>
     </row>
-    <row r="52" ht="48" customHeight="1">
+    <row r="52" ht="56" customHeight="1">
       <c r="B52" s="43" t="inlineStr">
         <is>
-          <t>Ночь 01.09–02.09</t>
+          <t>01.09–02.09 ночная (вт–ср)</t>
         </is>
       </c>
       <c r="C52" s="44" t="inlineStr">
         <is>
-          <t>Время на рабочем месте посчитано полностью (вход в чистую зону в 20:45:29, выход в 08:54:35). Фактического входа через турникет в журнале нет, есть только выход в 09:31:02, поэтому время на территории за эту смену неизвестно и в итог территории не входит.</t>
+          <t>В журнале нет фактического входа через турникет, поэтому время на территории не посчитано. Ранний уход с рабочего места на 5 мин 25 сек: выход из чистой зоны в 08:54:35 при окончании смены в 09:00. Далее выход с территории в 09:31:02. К началу смены на рабочем месте уже был (вход в чистую зону в 20:45:29).</t>
         </is>
       </c>
       <c r="D52" s="45" t="n"/>
@@ -1975,15 +1975,15 @@
       <c r="F52" s="45" t="n"/>
       <c r="G52" s="45" t="n"/>
     </row>
-    <row r="53" ht="48" customHeight="1">
+    <row r="53" ht="78" customHeight="1">
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>Утро 30.09</t>
+          <t>30.09 дневная (ср)</t>
         </is>
       </c>
       <c r="C53" s="44" t="inlineStr">
         <is>
-          <t>В 08:29:40 турникет записал фактический выход, а в 08:29:48 — фактический вход. Смена 29.09 уже была закрыта выходом в 21:01:09. Утренний «выход» не используется. Время на территории 30.09 считается от входа в 08:29:48 до выхода в 21:06:07.</t>
+          <t>30.09.2026 в 08:29:40 турникет записал фактический выход за несколько секунд до входа. Предыдущая смена уже закрыта, предшествующего входа нет. Этот выход не засчитан как уход с территории: похоже на повторное срабатывание или сбой. Ранний уход с рабочего места на 4 мин 19 сек: выход из чистой зоны в 20:55:41 при окончании смены в 21:00. Далее вход в гардероб в 21:01:24, выход с территории в 21:06:07. К началу смены на рабочем месте уже был (вход в чистую зону в 08:49:59).</t>
         </is>
       </c>
       <c r="D53" s="45" t="n"/>
@@ -1991,7 +1991,7 @@
       <c r="F53" s="45" t="n"/>
       <c r="G53" s="45" t="n"/>
     </row>
-    <row r="54" ht="48" customHeight="1">
+    <row r="54" ht="56" customHeight="1">
       <c r="B54" s="43" t="inlineStr">
         <is>
           <t>Дни без записей</t>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C54" s="44" t="inlineStr">
         <is>
-          <t>В выгрузке нет ни одного события за 03–04.09, 11–12.09, 15–21.09, 23.09 и 28.09, а также за начало смены 31.08. Это не записано как отсутствие: по этим датам журнал просто ничего не содержит.</t>
+          <t>В выгрузке нет ни одного события за 03.09–04.09, 11.09–12.09, 15.09–21.09, 23.09, 28.09. Это не записано как отсутствие: по этим датам журнал просто ничего не содержит.</t>
         </is>
       </c>
       <c r="D54" s="45" t="n"/>
@@ -2010,7 +2010,7 @@
     <row r="57">
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>Часы по сменам. Звёздочка у 31.08–01.09 — неполная смена, в общий итог не входит. Пустой столбец территории — нет входа через турникет.</t>
+          <t>Часы по сменам. Звёздочка — неполная смена, в общий итог не входит. Пустой столбец территории — нет входа или выхода через турникет.</t>
         </is>
       </c>
     </row>
@@ -2094,8 +2094,8 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
@@ -3327,53 +3327,53 @@
       <c r="A19" s="65" t="inlineStr"/>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>Итого по 14 полным сменам. Фрагмент 31.08–01.09 в сумму не входит.</t>
+          <t>Итого по 14 полным сменам. Строки «Неполные данные» в сумму не входят.</t>
         </is>
       </c>
       <c r="C19" s="65" t="n"/>
       <c r="D19" s="65" t="n"/>
       <c r="E19" s="65" t="n"/>
       <c r="F19" s="67">
-        <f>SUM(F4:F17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",F3:F17)</f>
         <v/>
       </c>
       <c r="G19" s="65" t="n"/>
       <c r="H19" s="65" t="n"/>
       <c r="I19" s="67">
-        <f>SUM(I4:I17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",I3:I17)</f>
         <v/>
       </c>
       <c r="J19" s="67">
-        <f>SUM(J4:J17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",J3:J17)</f>
         <v/>
       </c>
       <c r="K19" s="65" t="n"/>
       <c r="L19" s="67">
-        <f>SUM(L4:L17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",L3:L17)</f>
         <v/>
       </c>
       <c r="M19" s="67">
-        <f>SUM(M4:M17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",M3:M17)</f>
         <v/>
       </c>
       <c r="N19" s="67">
-        <f>SUM(N4:N17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",N3:N17)</f>
         <v/>
       </c>
       <c r="O19" s="67">
-        <f>SUM(O4:O17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",O3:O17)</f>
         <v/>
       </c>
       <c r="P19" s="67">
-        <f>SUM(P4:P17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",P3:P17)</f>
         <v/>
       </c>
       <c r="Q19" s="68">
-        <f>AVERAGE(Q4:Q17)</f>
+        <f>AVERAGE(Q3:Q17)</f>
         <v/>
       </c>
       <c r="R19" s="67">
-        <f>SUM(R4:R17)</f>
+        <f>SUMIF($K$3:$K$17,"&lt;&gt;Неполные данные",R3:R17)</f>
         <v/>
       </c>
       <c r="S19" s="65" t="n"/>
@@ -3382,7 +3382,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="B20" s="69" t="inlineStr">
         <is>
-          <t>Неполная ночь 31.08–01.09 в итог не включена: до выхода в 05:09:25 время неизвестно, после возвращения в 05:44:19 в чистой зоне ещё 3 ч 15 мин 20 сек. Сумма колонки «Ранний уход» включает и уходы короче одной минуты; как нарушение на листе «Итоги» посчитаны только уходы от 1 минуты.</t>
+          <t>Неполные смены в итог не включены: по ним не виден либо приход, либо уход. Сумма колонки «Ранний уход» включает и уходы короче одной минуты; как нарушение на листе «Итоги» посчитаны только уходы от 1 минуты.</t>
         </is>
       </c>
     </row>
@@ -10998,21 +10998,21 @@
     <row r="13" ht="48" customHeight="1">
       <c r="B13" s="92" t="inlineStr">
         <is>
-          <t>Ночь 31.08–01.09 обрезана началом файла. Известен только кусок с 05:44:19 до 08:59:39 плюс сам факт, что в 05:09:25 человек уже выходил из чистой зоны. Общий итог на этот кусок не опирается.</t>
+          <t>Если журнал начинается уже с выхода из чистой зоны или обрывается на входе без последующего выхода, смена помечена как неполные данные и не входит в общий итог. Известный кусок остаётся в строке этой смены.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="B14" s="92" t="inlineStr">
         <is>
-          <t>Ночь 01.09–02.09 не имеет входа через турникет. В итог территории она не включена, в итог рабочего места включена.</t>
+          <t>Если нет фактического входа через турникет, время на территории не считается. Выход через турникет за несколько секунд до входа, когда предыдущая смена уже закрыта, не принимается за уход с территории.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="B15" s="92" t="inlineStr">
         <is>
-          <t>Событие 30.09 в 08:29:40 («фактический выход» за 8 секунд до входа) не принято за уход с территории.</t>
+          <t>Если сотрудник пришёл утром, как на дневную смену, но ушёл задолго до 21:00, это всё равно дневная смена 09:00–21:00, а уход считается ранним.</t>
         </is>
       </c>
     </row>
